--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_2.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01187084111078365</v>
+        <v>0.004957783387703507</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008421866602520764</v>
+        <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9381757</v>
+        <v>4772423</v>
       </c>
       <c r="L2" t="n">
-        <v>5708072</v>
+        <v>2981114</v>
       </c>
       <c r="M2" t="n">
-        <v>1473745</v>
+        <v>776488</v>
       </c>
       <c r="N2" t="n">
-        <v>81049</v>
+        <v>43653</v>
       </c>
       <c r="O2" t="n">
-        <v>877446</v>
+        <v>458353</v>
       </c>
       <c r="P2" t="n">
-        <v>345970</v>
+        <v>177698</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999974370002747</v>
+        <v>0.9999958872795105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9385031461715698</v>
+        <v>0.9564840197563171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8587761521339417</v>
+        <v>0.8849969506263733</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8156130313873291</v>
+        <v>0.8684829473495483</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6407896876335144</v>
+        <v>0.6957873106002808</v>
       </c>
       <c r="V2" t="n">
-        <v>0.859171450138092</v>
+        <v>0.8961659073829651</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9050148725509644</v>
+        <v>0.9339107275009155</v>
       </c>
       <c r="X2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9612236</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5914772</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1596616</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117783</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917498</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.956666111946106</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112259149551392</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582807779312134</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.662726104259491</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020707607269287</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,425 +786,425 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002762649949978431</v>
+        <v>0.001124300870728883</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002020252121303941</v>
+        <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9381757</v>
+        <v>4772423</v>
       </c>
       <c r="E3" t="n">
-        <v>643151</v>
+        <v>259361</v>
       </c>
       <c r="F3" t="n">
-        <v>10674</v>
+        <v>1838</v>
       </c>
       <c r="G3" t="n">
-        <v>1434</v>
+        <v>423</v>
       </c>
       <c r="H3" t="n">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>19980214</v>
+        <v>10016596</v>
       </c>
       <c r="K3" t="n">
-        <v>21920718</v>
+        <v>11078337</v>
       </c>
       <c r="L3" t="n">
-        <v>25134369</v>
+        <v>12682859</v>
       </c>
       <c r="M3" t="n">
-        <v>30378407</v>
+        <v>15280202</v>
       </c>
       <c r="N3" t="n">
-        <v>32349502</v>
+        <v>16221450</v>
       </c>
       <c r="O3" t="n">
-        <v>31411439</v>
+        <v>15767520</v>
       </c>
       <c r="P3" t="n">
-        <v>32149944</v>
+        <v>16123743</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9346867203712463</v>
+        <v>0.9480119347572327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8781985640525818</v>
+        <v>0.9146336913108826</v>
       </c>
       <c r="T3" t="n">
-        <v>0.791816234588623</v>
+        <v>0.8333097100257874</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4556796252727509</v>
+        <v>0.4901306927204132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8623234629631042</v>
+        <v>0.9005448222160339</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8950316309928894</v>
+        <v>0.9193717241287231</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9612236</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>394430</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>16993</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13519</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>19980246</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22100069</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25496816</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30447946</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32334994</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31455659</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32159747</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576488733291626</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099997878074646</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578325510025024</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622081995010376</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016851186752319</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03927457626061116</v>
+        <v>0.02099358837181096</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03187636554403791</v>
+        <v>0.03184710126109398</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>579137</v>
+        <v>202676</v>
       </c>
       <c r="E4" t="n">
-        <v>5708072</v>
+        <v>2981114</v>
       </c>
       <c r="F4" t="n">
-        <v>201013</v>
+        <v>73334</v>
       </c>
       <c r="G4" t="n">
-        <v>3980</v>
+        <v>1026</v>
       </c>
       <c r="H4" t="n">
-        <v>7179</v>
+        <v>1167</v>
       </c>
       <c r="I4" t="n">
-        <v>370</v>
+        <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K4" t="n">
-        <v>614754</v>
+        <v>217125</v>
       </c>
       <c r="L4" t="n">
-        <v>938680</v>
+        <v>387388</v>
       </c>
       <c r="M4" t="n">
-        <v>333172</v>
+        <v>117586</v>
       </c>
       <c r="N4" t="n">
-        <v>45434</v>
+        <v>19086</v>
       </c>
       <c r="O4" t="n">
-        <v>143824</v>
+        <v>53107</v>
       </c>
       <c r="P4" t="n">
-        <v>36311</v>
+        <v>12575</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999987483024597</v>
+        <v>0.9999979138374329</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9365910291671753</v>
+        <v>0.9522291421890259</v>
       </c>
       <c r="S4" t="n">
-        <v>0.868378758430481</v>
+        <v>0.8995712399482727</v>
       </c>
       <c r="T4" t="n">
-        <v>0.80353844165802</v>
+        <v>0.8505327701568604</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5326091647148132</v>
+        <v>0.5751270055770874</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8607445955276489</v>
+        <v>0.8983500599861145</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8999955654144287</v>
+        <v>0.9265841841697693</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>406497</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5914772</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165124</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10938</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>435403</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>576233</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263633</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>59942</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99604</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571572542190552</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106124639511108</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580566048622131</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624670624732971</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018778800964355</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>20332</v>
+        <v>8344</v>
       </c>
       <c r="E5" t="n">
-        <v>262349</v>
+        <v>108510</v>
       </c>
       <c r="F5" t="n">
-        <v>1473745</v>
+        <v>776488</v>
       </c>
       <c r="G5" t="n">
-        <v>21084</v>
+        <v>8891</v>
       </c>
       <c r="H5" t="n">
-        <v>80833</v>
+        <v>29019</v>
       </c>
       <c r="I5" t="n">
-        <v>2876</v>
+        <v>559</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>655571</v>
+        <v>261715</v>
       </c>
       <c r="L5" t="n">
-        <v>791679</v>
+        <v>278239</v>
       </c>
       <c r="M5" t="n">
-        <v>387476</v>
+        <v>155324</v>
       </c>
       <c r="N5" t="n">
-        <v>96815</v>
+        <v>45411</v>
       </c>
       <c r="O5" t="n">
-        <v>140091</v>
+        <v>50620</v>
       </c>
       <c r="P5" t="n">
-        <v>40575</v>
+        <v>15584</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999990463256836</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9610004425048828</v>
+        <v>0.9706765413284302</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9468771815299988</v>
+        <v>0.9592379927635193</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9778757691383362</v>
+        <v>0.9832873940467834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9956328868865967</v>
+        <v>0.9960502982139587</v>
       </c>
       <c r="V5" t="n">
-        <v>0.991283655166626</v>
+        <v>0.9936479330062866</v>
       </c>
       <c r="W5" t="n">
-        <v>0.997639536857605</v>
+        <v>0.9982755780220032</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15948</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169377</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1596616</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19836</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58178</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>425092</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>584979</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264605</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60081</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100039</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97358238697052</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643502831459045</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837828278541565</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963152408599854</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938708543777466</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983717799186707</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>15205</v>
+        <v>6069</v>
       </c>
       <c r="E6" t="n">
-        <v>26838</v>
+        <v>18629</v>
       </c>
       <c r="F6" t="n">
-        <v>36102</v>
+        <v>12432</v>
       </c>
       <c r="G6" t="n">
-        <v>81049</v>
+        <v>43653</v>
       </c>
       <c r="H6" t="n">
-        <v>17551</v>
+        <v>7916</v>
       </c>
       <c r="I6" t="n">
-        <v>1109</v>
+        <v>357</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12847</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10646</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21693</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117783</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13933</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>5992</v>
+        <v>795</v>
       </c>
       <c r="F7" t="n">
-        <v>83827</v>
+        <v>29642</v>
       </c>
       <c r="G7" t="n">
-        <v>18285</v>
+        <v>8535</v>
       </c>
       <c r="H7" t="n">
-        <v>877446</v>
+        <v>458353</v>
       </c>
       <c r="I7" t="n">
-        <v>31930</v>
+        <v>11615</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1618</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59163</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15119</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917498</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>350</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>1556</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>651</v>
+        <v>211</v>
       </c>
       <c r="H8" t="n">
-        <v>37978</v>
+        <v>14922</v>
       </c>
       <c r="I8" t="n">
-        <v>345970</v>
+        <v>177698</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
